--- a/research/traditional_assets/database/data/botswana/botswana_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/botswana/botswana_financial_svcs_non_bank_insurance.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.108</v>
+        <v>0.07769999999999999</v>
       </c>
       <c r="E2">
-        <v>-0.0214</v>
+        <v>0.0301</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>58.1</v>
+        <v>48.8</v>
       </c>
       <c r="L2">
-        <v>0.2406793703396852</v>
+        <v>0.2512873326467559</v>
       </c>
       <c r="M2">
-        <v>23.8</v>
+        <v>33.2</v>
       </c>
       <c r="N2">
-        <v>0.09370078740157481</v>
+        <v>0.158472553699284</v>
       </c>
       <c r="O2">
-        <v>0.4096385542168675</v>
+        <v>0.6803278688524591</v>
       </c>
       <c r="P2">
-        <v>23.8</v>
+        <v>33.2</v>
       </c>
       <c r="Q2">
-        <v>0.09370078740157481</v>
+        <v>0.158472553699284</v>
       </c>
       <c r="R2">
-        <v>0.4096385542168675</v>
+        <v>0.6803278688524591</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>92.09999999999999</v>
+        <v>106.5</v>
       </c>
       <c r="V2">
-        <v>0.3625984251968504</v>
+        <v>0.5083532219570406</v>
       </c>
       <c r="W2">
-        <v>0.1632022471910112</v>
+        <v>0.1128323699421965</v>
       </c>
       <c r="X2">
-        <v>0.04305268062584232</v>
+        <v>0.08592039924645387</v>
       </c>
       <c r="Y2">
-        <v>0.1201495665651689</v>
+        <v>0.02691197069574267</v>
       </c>
       <c r="Z2">
-        <v>0.3400191560087892</v>
+        <v>0.2147849938064059</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03551224860456217</v>
+        <v>0.0566650229109578</v>
       </c>
       <c r="AC2">
-        <v>-0.03551224860456217</v>
+        <v>-0.0566650229109578</v>
       </c>
       <c r="AD2">
-        <v>569.9</v>
+        <v>735.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>569.9</v>
+        <v>735.8</v>
       </c>
       <c r="AG2">
-        <v>477.8</v>
+        <v>629.3</v>
       </c>
       <c r="AH2">
-        <v>0.6917101589998786</v>
+        <v>0.7783772347402941</v>
       </c>
       <c r="AI2">
-        <v>0.5467191097467382</v>
+        <v>0.6193602693602693</v>
       </c>
       <c r="AJ2">
-        <v>0.6529106313200328</v>
+        <v>0.7502384358607534</v>
       </c>
       <c r="AK2">
-        <v>0.5027885930758708</v>
+        <v>0.5818770226537217</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.108</v>
+        <v>0.07769999999999999</v>
       </c>
       <c r="E3">
-        <v>-0.0214</v>
+        <v>0.0301</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>58.1</v>
+        <v>48.8</v>
       </c>
       <c r="L3">
-        <v>0.2406793703396852</v>
+        <v>0.2512873326467559</v>
       </c>
       <c r="M3">
-        <v>23.8</v>
+        <v>33.2</v>
       </c>
       <c r="N3">
-        <v>0.09370078740157481</v>
+        <v>0.158472553699284</v>
       </c>
       <c r="O3">
-        <v>0.4096385542168675</v>
+        <v>0.6803278688524591</v>
       </c>
       <c r="P3">
-        <v>23.8</v>
+        <v>33.2</v>
       </c>
       <c r="Q3">
-        <v>0.09370078740157481</v>
+        <v>0.158472553699284</v>
       </c>
       <c r="R3">
-        <v>0.4096385542168675</v>
+        <v>0.6803278688524591</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>92.09999999999999</v>
+        <v>106.5</v>
       </c>
       <c r="V3">
-        <v>0.3625984251968504</v>
+        <v>0.5083532219570406</v>
       </c>
       <c r="W3">
-        <v>0.1632022471910112</v>
+        <v>0.1128323699421965</v>
       </c>
       <c r="X3">
-        <v>0.04305268062584232</v>
+        <v>0.08592039924645387</v>
       </c>
       <c r="Y3">
-        <v>0.1201495665651689</v>
+        <v>0.02691197069574267</v>
       </c>
       <c r="Z3">
-        <v>0.3400191560087892</v>
+        <v>0.2147849938064059</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03551224860456217</v>
+        <v>0.0566650229109578</v>
       </c>
       <c r="AC3">
-        <v>-0.03551224860456217</v>
+        <v>-0.0566650229109578</v>
       </c>
       <c r="AD3">
-        <v>569.9</v>
+        <v>735.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>569.9</v>
+        <v>735.8</v>
       </c>
       <c r="AG3">
-        <v>477.8</v>
+        <v>629.3</v>
       </c>
       <c r="AH3">
-        <v>0.6917101589998786</v>
+        <v>0.7783772347402941</v>
       </c>
       <c r="AI3">
-        <v>0.5467191097467382</v>
+        <v>0.6193602693602693</v>
       </c>
       <c r="AJ3">
-        <v>0.6529106313200328</v>
+        <v>0.7502384358607534</v>
       </c>
       <c r="AK3">
-        <v>0.5027885930758708</v>
+        <v>0.5818770226537217</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/botswana/botswana_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/botswana/botswana_financial_svcs_non_bank_insurance.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07769999999999999</v>
+        <v>-0.00596</v>
       </c>
       <c r="E2">
-        <v>0.0301</v>
+        <v>-0.105</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>48.8</v>
+        <v>27.6</v>
       </c>
       <c r="L2">
-        <v>0.2512873326467559</v>
+        <v>0.1987041036717063</v>
       </c>
       <c r="M2">
-        <v>33.2</v>
+        <v>24.8</v>
       </c>
       <c r="N2">
-        <v>0.158472553699284</v>
+        <v>0.1232604373757455</v>
       </c>
       <c r="O2">
-        <v>0.6803278688524591</v>
+        <v>0.8985507246376812</v>
       </c>
       <c r="P2">
-        <v>33.2</v>
+        <v>24.8</v>
       </c>
       <c r="Q2">
-        <v>0.158472553699284</v>
+        <v>0.1232604373757455</v>
       </c>
       <c r="R2">
-        <v>0.6803278688524591</v>
+        <v>0.8985507246376812</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>106.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="V2">
-        <v>0.5083532219570406</v>
+        <v>0.3946322067594434</v>
       </c>
       <c r="W2">
-        <v>0.1128323699421965</v>
+        <v>0.06618705035971223</v>
       </c>
       <c r="X2">
-        <v>0.08592039924645387</v>
+        <v>0.09601715184298062</v>
       </c>
       <c r="Y2">
-        <v>0.02691197069574267</v>
+        <v>-0.0298301014832684</v>
       </c>
       <c r="Z2">
-        <v>0.2147849938064059</v>
+        <v>0.1334409314926363</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0566650229109578</v>
+        <v>0.06164810593096645</v>
       </c>
       <c r="AC2">
-        <v>-0.0566650229109578</v>
+        <v>-0.06164810593096645</v>
       </c>
       <c r="AD2">
-        <v>735.8</v>
+        <v>712</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>735.8</v>
+        <v>712</v>
       </c>
       <c r="AG2">
-        <v>629.3</v>
+        <v>632.6</v>
       </c>
       <c r="AH2">
-        <v>0.7783772347402941</v>
+        <v>0.7796758650897941</v>
       </c>
       <c r="AI2">
-        <v>0.6193602693602693</v>
+        <v>0.6361118556240508</v>
       </c>
       <c r="AJ2">
-        <v>0.7502384358607534</v>
+        <v>0.7586951307267931</v>
       </c>
       <c r="AK2">
-        <v>0.5818770226537217</v>
+        <v>0.608327723819598</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07769999999999999</v>
+        <v>-0.00596</v>
       </c>
       <c r="E3">
-        <v>0.0301</v>
+        <v>-0.105</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>48.8</v>
+        <v>27.6</v>
       </c>
       <c r="L3">
-        <v>0.2512873326467559</v>
+        <v>0.1987041036717063</v>
       </c>
       <c r="M3">
-        <v>33.2</v>
+        <v>24.8</v>
       </c>
       <c r="N3">
-        <v>0.158472553699284</v>
+        <v>0.1232604373757455</v>
       </c>
       <c r="O3">
-        <v>0.6803278688524591</v>
+        <v>0.8985507246376812</v>
       </c>
       <c r="P3">
-        <v>33.2</v>
+        <v>24.8</v>
       </c>
       <c r="Q3">
-        <v>0.158472553699284</v>
+        <v>0.1232604373757455</v>
       </c>
       <c r="R3">
-        <v>0.6803278688524591</v>
+        <v>0.8985507246376812</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>106.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="V3">
-        <v>0.5083532219570406</v>
+        <v>0.3946322067594434</v>
       </c>
       <c r="W3">
-        <v>0.1128323699421965</v>
+        <v>0.06618705035971223</v>
       </c>
       <c r="X3">
-        <v>0.08592039924645387</v>
+        <v>0.09601715184298062</v>
       </c>
       <c r="Y3">
-        <v>0.02691197069574267</v>
+        <v>-0.0298301014832684</v>
       </c>
       <c r="Z3">
-        <v>0.2147849938064059</v>
+        <v>0.1334409314926363</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0566650229109578</v>
+        <v>0.06164810593096645</v>
       </c>
       <c r="AC3">
-        <v>-0.0566650229109578</v>
+        <v>-0.06164810593096645</v>
       </c>
       <c r="AD3">
-        <v>735.8</v>
+        <v>712</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>735.8</v>
+        <v>712</v>
       </c>
       <c r="AG3">
-        <v>629.3</v>
+        <v>632.6</v>
       </c>
       <c r="AH3">
-        <v>0.7783772347402941</v>
+        <v>0.7796758650897941</v>
       </c>
       <c r="AI3">
-        <v>0.6193602693602693</v>
+        <v>0.6361118556240508</v>
       </c>
       <c r="AJ3">
-        <v>0.7502384358607534</v>
+        <v>0.7586951307267931</v>
       </c>
       <c r="AK3">
-        <v>0.5818770226537217</v>
+        <v>0.608327723819598</v>
       </c>
       <c r="AL3">
         <v>0</v>
